--- a/output/roomself_excel/50.xlsx
+++ b/output/roomself_excel/50.xlsx
@@ -479,7 +479,7 @@
         <v>907</v>
       </c>
       <c r="F2" t="n">
-        <v>750</v>
+        <v>473</v>
       </c>
     </row>
     <row r="3">
@@ -608,10 +608,10 @@
         <v>4564</v>
       </c>
       <c r="E8" t="n">
-        <v>910</v>
+        <v>748</v>
       </c>
       <c r="F8" t="n">
-        <v>748</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9">
@@ -743,7 +743,7 @@
         <v>551</v>
       </c>
       <c r="F14" t="n">
-        <v>493</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15">
@@ -850,10 +850,10 @@
         <v>1800</v>
       </c>
       <c r="E19" t="n">
-        <v>912</v>
+        <v>219</v>
       </c>
       <c r="F19" t="n">
-        <v>258</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20">
@@ -938,10 +938,10 @@
         <v>3940</v>
       </c>
       <c r="E23" t="n">
-        <v>719</v>
+        <v>460</v>
       </c>
       <c r="F23" t="n">
-        <v>394</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24">

--- a/output/roomself_excel/50.xlsx
+++ b/output/roomself_excel/50.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,11 +510,38 @@
       <c r="D2" t="n">
         <v>6992</v>
       </c>
-      <c r="E2" t="n">
-        <v>907</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>473</v>
+        <v>777</v>
+      </c>
+      <c r="G2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>332</v>
+      </c>
+      <c r="J2" t="n">
+        <v>21</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>450</v>
+      </c>
+      <c r="M2" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +559,23 @@
       <c r="D3" t="n">
         <v>516</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>53</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>23</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +592,31 @@
       <c r="D4" t="n">
         <v>648</v>
       </c>
-      <c r="E4" t="n">
-        <v>116</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>89</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="G4" t="n">
+        <v>21</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>95</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +633,23 @@
       <c r="D5" t="n">
         <v>596</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>54</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>21</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +666,23 @@
       <c r="D6" t="n">
         <v>616</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>59</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>21</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +699,23 @@
       <c r="D7" t="n">
         <v>756</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>94</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>21</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +732,31 @@
       <c r="D8" t="n">
         <v>4564</v>
       </c>
-      <c r="E8" t="n">
-        <v>748</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
+        <v>186</v>
+      </c>
+      <c r="G8" t="n">
+        <v>21</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>230</v>
       </c>
+      <c r="J8" t="n">
+        <v>22</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +773,31 @@
       <c r="D9" t="n">
         <v>1676</v>
       </c>
-      <c r="E9" t="n">
-        <v>354</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>108</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="G9" t="n">
+        <v>21</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>87</v>
+      </c>
+      <c r="J9" t="n">
+        <v>22</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +814,23 @@
       <c r="D10" t="n">
         <v>2324</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>349</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>22</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +847,23 @@
       <c r="D11" t="n">
         <v>3248</v>
       </c>
-      <c r="E11" t="n">
-        <v>632</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>238</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="G11" t="n">
+        <v>22</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +880,31 @@
       <c r="D12" t="n">
         <v>2684</v>
       </c>
-      <c r="E12" t="n">
-        <v>376</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>337</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="G12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>316</v>
+      </c>
+      <c r="J12" t="n">
+        <v>21</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +921,15 @@
       <c r="D13" t="n">
         <v>728</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +946,31 @@
       <c r="D14" t="n">
         <v>3352</v>
       </c>
-      <c r="E14" t="n">
-        <v>551</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>255</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="G14" t="n">
+        <v>23</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>146</v>
+      </c>
+      <c r="J14" t="n">
+        <v>21</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +987,31 @@
       <c r="D15" t="n">
         <v>2064</v>
       </c>
-      <c r="E15" t="n">
-        <v>254</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>146</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="G15" t="n">
+        <v>22</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>112</v>
+      </c>
+      <c r="J15" t="n">
+        <v>22</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1028,23 @@
       <c r="D16" t="n">
         <v>1080</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>160</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>22</v>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1061,31 @@
       <c r="D17" t="n">
         <v>1544</v>
       </c>
-      <c r="E17" t="n">
-        <v>332</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>98</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="G17" t="n">
+        <v>22</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>310</v>
+      </c>
+      <c r="J17" t="n">
+        <v>22</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,11 +1102,38 @@
       <c r="D18" t="n">
         <v>2296</v>
       </c>
-      <c r="E18" t="n">
-        <v>405</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>236</v>
+        <v>213</v>
+      </c>
+      <c r="G18" t="n">
+        <v>21</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>213</v>
+      </c>
+      <c r="J18" t="n">
+        <v>23</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>361</v>
+      </c>
+      <c r="M18" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="19">
@@ -849,12 +1151,23 @@
       <c r="D19" t="n">
         <v>1800</v>
       </c>
-      <c r="E19" t="n">
-        <v>219</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>44</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="G19" t="n">
+        <v>43</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1184,23 @@
       <c r="D20" t="n">
         <v>1348</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>144</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>43</v>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1217,31 @@
       <c r="D21" t="n">
         <v>1436</v>
       </c>
-      <c r="E21" t="n">
-        <v>236</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F21" t="n">
-        <v>210</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="G21" t="n">
+        <v>43</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>193</v>
+      </c>
+      <c r="J21" t="n">
+        <v>44</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,11 +1258,38 @@
       <c r="D22" t="n">
         <v>3512</v>
       </c>
-      <c r="E22" t="n">
-        <v>742</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>269</v>
+        <v>224</v>
+      </c>
+      <c r="G22" t="n">
+        <v>43</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>654</v>
+      </c>
+      <c r="J22" t="n">
+        <v>45</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>224</v>
+      </c>
+      <c r="M22" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="23">
@@ -937,12 +1307,23 @@
       <c r="D23" t="n">
         <v>3940</v>
       </c>
-      <c r="E23" t="n">
-        <v>460</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F23" t="n">
+        <v>452</v>
+      </c>
+      <c r="G23" t="n">
         <v>44</v>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1340,23 @@
       <c r="D24" t="n">
         <v>2504</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
         <v>200</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>45</v>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,11 +1373,38 @@
       <c r="D25" t="n">
         <v>2120</v>
       </c>
-      <c r="E25" t="n">
-        <v>419</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F25" t="n">
         <v>200</v>
+      </c>
+      <c r="G25" t="n">
+        <v>44</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>199</v>
+      </c>
+      <c r="J25" t="n">
+        <v>45</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>330</v>
+      </c>
+      <c r="M25" t="n">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
